--- a/data/google_news_dedup_audit_29_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_29_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,442 +445,484 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.709650993347168</v>
+        <v>0.8795360922813416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amazon Connect expands into a set of agentic AI solutions - About Amazon</t>
+          <t>Amazon launches 1-hour delivery in hundreds of US cities - MSN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon Web Services unveils agentic AI supply chain tool - Supply Chain Dive</t>
+          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5869574546813965</v>
+        <v>0.6853862404823303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
+          <t>Amazon launches 1-hour delivery in hundreds of US cities - MSN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Amazon scales its quick delivery service ‘Amazon Now’ in 100 cities - MediaNama</t>
+          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7807619571685791</v>
+        <v>0.4852896928787231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
+          <t>Two Jewish people stabbed in London amid rising antisemitic attacks - CNN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7881379127502441</v>
+        <v>0.5387002825737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Amazon speeds up delivery with 1-hour, 3-hour options in hundreds of cities - MSN</t>
+          <t>Breaking: Two Jewish men reportedly injured after stabbing in north London - Australian Broadcasting Corporation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7763246297836304</v>
+        <v>0.4732542634010315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
+          <t>Two stabbed in Golders Green, north-west London, says Jewish group - The Guardian</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7107405662536621</v>
+        <v>0.4943191707134247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Slachtoffer steekpartij Merksplas is buiten levensgevaar, verdachte (22) slaat tolk tijdens verhoor - Nieuwsblad</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Verdachte steekpartij in Merksplas slaat Roemeense tolk in gezicht en is aangehouden - VRT</t>
+          <t>Two Jewish Londoners stabbed in 'appalling' attack - Reuters</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7168146371841431</v>
+        <v>0.4746301174163818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Slachtoffer steekpartij Merksplas is buiten levensgevaar, verdachte (22) slaat tolk tijdens verhoor - Nieuwsblad</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Verdachte van moordpoging in Merksplas gaat tolk te lijf tijdens verhoor: “Slachtoffer ernstig gewond” - HLN</t>
+          <t>Two Jewish people stabbed in 'appalling' London attack - NBC News</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9425693154335022</v>
+        <v>0.4574146270751953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Slachtoffer steekpartij Merksplas is buiten levensgevaar, verdachte (22) slaat tolk tijdens verhoor - Nieuwsblad</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slachtoffer steekpartij Merksplas buiten levensgevaar, verdachte (22) slaat tolk tijdens verhoor - GVA</t>
+          <t>2 People Stabbed in North London, Jewish Charity Says - The New York Times</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8716336488723755</v>
+        <v>0.7571534514427185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Arbeider in kritieke toestand na zware explosie bij tuinbouwbedrijf in Duffel - HLN</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Twee arbeiders gewond na zware explosie bij tuinbouwbedrijf in Duffel - HLN</t>
+          <t>Man arrested after stabbing 2 people in north London, Jewish volunteer security group says - CBS News</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8713790774345398</v>
+        <v>0.3685643076896667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Haiti's Rare Plant Zone May Disappear in 50 Years - Mirage News</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haiti’s ‘Goldilocks Zone’ for rare plants could vanish in 50 years, researchers say - Florida International University</t>
+          <t>Starmer condemns wave of attacks on Jewish targets after 2 stabbed in London - The Washington Post</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7115242481231689</v>
+        <v>0.4968286156654358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Man taken to hospital after stabbing near busy road in Leytonstone - Guardian Series</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Man taken to hospital after stabbing near war memorial - London Now</t>
+          <t>2 Injured in Golders Green London Stabbing Attack; Suspect Targeted Jews, Patrol Group Says - The Media Line</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7001162767410278</v>
+        <v>0.4054416418075562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Corteo del 25 aprile: la Comunità ebraica di Milano chiede un chiarimento al sindaco Sala - mosaico-cem.it</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Milano, Brigata Ebraica: non rinunceremo al corteo - agenziagiornalisticaopinione.it</t>
+          <t>2 Jews injured in stabbing attack in London's Golders Green, says emergency response group - The Times of Israel</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7635656595230103</v>
+        <v>0.5603243112564087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Incidente sulla A1 tra Valdichiana e Monte San Savino: tir perde… - sr71.it</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Incidente A1 oggi: 9 km di coda tra Valdichiana e Monte San Savino - SICURAUTO.it</t>
+          <t>UK leaders condemn stabbing of two Jews in London amid rising antisemitic incidents - ynetnews</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
-        <v>0.562788188457489</v>
+        <v>0.4531742334365845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Incidente sulla A1 tra Valdichiana e Monte San Savino: tir perde… - sr71.it</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incidente A14 oggi: ancora 7 km di coda tra Pesaro e Marotta - SICURAUTO.it</t>
+          <t>Starmer condemns London stabbing attack in Jewish neighbourhood - SMH.com.au</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7392920255661011</v>
+        <v>0.4674909114837646</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grave incidente in A1, autoarticolato perde il carico che travolge una vettura - daicollifiorentini.it</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Autostrada A1, tir perde il carico che finisce contro un’auto: feriti gravemente due giovani - Il Tirreno</t>
+          <t>Antisemitic stabbing in London's Golders Green - www.israelhayom.com</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7307569980621338</v>
+        <v>0.5155401825904846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Grave incidente in A1, autoarticolato perde il carico che travolge una vettura - daicollifiorentini.it</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Salerno, grave incidente in autostrada: scontro tra due veicoli, tre feriti in ospedale - Il Mattino</t>
+          <t>Two Jewish Men Seriously Wounded in Stabbing in London's Golders Green - Haaretz</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="B18" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7277825474739075</v>
+        <v>0.6917082071304321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Auto travolta dal carico di un tir sull'A1: due giovani in ospedale - Corriere di Siena</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>INCIDENTE IN A1, CAMION PERDE MATERIALE CHE TRAVOLGE UN'AUTO: DUE FERITI - OK Siena</t>
+          <t>Counter-terror police investigate stabbing of two Jewish men in London - The Independent</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6680363416671753</v>
+        <v>0.7488348484039307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Traffico in A1 deviato in Toscana per incidente, Tir ha perso carico - ANSA</t>
+          <t>British police say man arrested over attempted London stabbing; two hospitalized in stable condition - The Times of Israel</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B20" t="n">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6149948239326477</v>
+        <v>0.6557744741439819</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Incidente sulla A19: Tir carico d’acqua si ribalta a Gerbini, traffico in tilt verso Catania - ViviEnna</t>
+          <t>London Stabbing: Two Injured In Knife Attack On Jewish Pedestrians, Suspect Arrested - i24NEWS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B21" t="n">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8313946723937988</v>
+        <v>0.5837048292160034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Marotta, incidente in autostrada poco dopo le 14: traffico bloccato, coda di 4 km. Si consiglia di uscire a Pesaro - Corriere Adriatico</t>
+          <t>Knife attack in London, 2 Jewish men injured in targeted stabbing - Firstpost</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="B22" t="n">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8404203653335571</v>
+        <v>0.4963404536247253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marotta, incidente in autostrada poco dopo le 14: traffico bloccato, coda di 3 km - Corriere Adriatico</t>
+          <t>London stabbing: Two injured in Jewish neighbourhood; Starmer calls attack ‘deeply concerning’ - The Times of India</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" t="n">
+        <v>45</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.3627550601959229</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>UK’s Starmer says stabbing in London’s Golders Green ‘deeply concerning’ - The Times of Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>49</v>
+      </c>
+      <c r="B24" t="n">
+        <v>54</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9999999403953552</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
         </is>
       </c>
     </row>

--- a/data/google_news_dedup_audit_29_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_29_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,55 +445,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8795360922813416</v>
+        <v>0.4852896928787231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amazon launches 1-hour delivery in hundreds of US cities - MSN</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
+          <t>Two Jewish people stabbed in London amid rising antisemitic attacks - CNN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6853862404823303</v>
+        <v>0.5387002825737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Amazon launches 1-hour delivery in hundreds of US cities - MSN</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
+          <t>Breaking: Two Jewish men reportedly injured after stabbing in north London - Australian Broadcasting Corporation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4852896928787231</v>
+        <v>0.4943191707134247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -502,19 +502,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Two Jewish people stabbed in London amid rising antisemitic attacks - CNN</t>
+          <t>Two Jewish Londoners stabbed in 'appalling' attack - Reuters</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5387002825737</v>
+        <v>0.4746301174163818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -523,19 +523,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Breaking: Two Jewish men reportedly injured after stabbing in north London - Australian Broadcasting Corporation</t>
+          <t>Two Jewish people stabbed in 'appalling' London attack - NBC News</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4732542634010315</v>
+        <v>0.4574146270751953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Two stabbed in Golders Green, north-west London, says Jewish group - The Guardian</t>
+          <t>2 People Stabbed in North London, Jewish Charity Says - The New York Times</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4943191707134247</v>
+        <v>0.7571534514427185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -565,19 +565,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Two Jewish Londoners stabbed in 'appalling' attack - Reuters</t>
+          <t>Man arrested after stabbing 2 people in north London, Jewish volunteer security group says - CBS News</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4746301174163818</v>
+        <v>0.3685643076896667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Two Jewish people stabbed in 'appalling' London attack - NBC News</t>
+          <t>Starmer condemns wave of attacks on Jewish targets after 2 stabbed in London - The Washington Post</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4574146270751953</v>
+        <v>0.4968286156654358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -607,19 +607,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2 People Stabbed in North London, Jewish Charity Says - The New York Times</t>
+          <t>2 Injured in Golders Green London Stabbing Attack; Suspect Targeted Jews, Patrol Group Says - The Media Line</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7571534514427185</v>
+        <v>0.4054416418075562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -628,19 +628,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Man arrested after stabbing 2 people in north London, Jewish volunteer security group says - CBS News</t>
+          <t>2 Jews injured in stabbing attack in London's Golders Green, says emergency response group - The Times of Israel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3685643076896667</v>
+        <v>0.4732542634010315</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -649,19 +649,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Starmer condemns wave of attacks on Jewish targets after 2 stabbed in London - The Washington Post</t>
+          <t>Two stabbed in Golders Green, north-west London, says Jewish group - The Guardian</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4968286156654358</v>
+        <v>0.5603243112564087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -670,19 +670,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2 Injured in Golders Green London Stabbing Attack; Suspect Targeted Jews, Patrol Group Says - The Media Line</t>
+          <t>UK leaders condemn stabbing of two Jews in London amid rising antisemitic incidents - ynetnews</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4054416418075562</v>
+        <v>0.4531742334365845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -691,19 +691,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2 Jews injured in stabbing attack in London's Golders Green, says emergency response group - The Times of Israel</t>
+          <t>Starmer condemns London stabbing attack in Jewish neighbourhood - SMH.com.au</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5603243112564087</v>
+        <v>0.4674909114837646</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -712,19 +712,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UK leaders condemn stabbing of two Jews in London amid rising antisemitic incidents - ynetnews</t>
+          <t>Antisemitic stabbing in London's Golders Green - www.israelhayom.com</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4531742334365845</v>
+        <v>0.5155401825904846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -733,19 +733,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Starmer condemns London stabbing attack in Jewish neighbourhood - SMH.com.au</t>
+          <t>Two Jewish Men Seriously Wounded in Stabbing in London's Golders Green - Haaretz</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4674909114837646</v>
+        <v>0.6917082071304321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -754,19 +754,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Antisemitic stabbing in London's Golders Green - www.israelhayom.com</t>
+          <t>Counter-terror police investigate stabbing of two Jewish men in London - The Independent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5155401825904846</v>
+        <v>0.7488348484039307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -775,19 +775,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Two Jewish Men Seriously Wounded in Stabbing in London's Golders Green - Haaretz</t>
+          <t>British police say man arrested over attempted London stabbing; two hospitalized in stable condition - The Times of Israel</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6917082071304321</v>
+        <v>0.6557744741439819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -796,19 +796,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Counter-terror police investigate stabbing of two Jewish men in London - The Independent</t>
+          <t>London Stabbing: Two Injured In Knife Attack On Jewish Pedestrians, Suspect Arrested - i24NEWS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7488348484039307</v>
+        <v>0.5837048292160034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -817,19 +817,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>British police say man arrested over attempted London stabbing; two hospitalized in stable condition - The Times of Israel</t>
+          <t>Knife attack in London, 2 Jewish men injured in targeted stabbing - Firstpost</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6557744741439819</v>
+        <v>0.4963404536247253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -838,19 +838,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>London Stabbing: Two Injured In Knife Attack On Jewish Pedestrians, Suspect Arrested - i24NEWS</t>
+          <t>London stabbing: Two injured in Jewish neighbourhood; Starmer calls attack ‘deeply concerning’ - The Times of India</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5837048292160034</v>
+        <v>0.3627550601959229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -859,68 +859,26 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Knife attack in London, 2 Jewish men injured in targeted stabbing - Firstpost</t>
+          <t>UK’s Starmer says stabbing in London’s Golders Green ‘deeply concerning’ - The Times of Israel</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4963404536247253</v>
+        <v>0.9999999403953552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
+          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>London stabbing: Two injured in Jewish neighbourhood; Starmer calls attack ‘deeply concerning’ - The Times of India</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B23" t="n">
-        <v>45</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.3627550601959229</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>UK’s Starmer says stabbing in London’s Golders Green ‘deeply concerning’ - The Times of Israel</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>49</v>
-      </c>
-      <c r="B24" t="n">
-        <v>54</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.9999999403953552</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
         <is>
           <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
         </is>
